--- a/NOW.xlsx
+++ b/NOW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4FC35F-AA99-4A1D-9B5E-88C84E62265B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574C674D-AF1D-4CD3-A9E8-0DF9FC84AF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51495" yWindow="570" windowWidth="29955" windowHeight="20700" xr2:uid="{04F796B3-9D76-4BC0-BCDC-4708D1ACB929}"/>
+    <workbookView xWindow="10810" yWindow="4180" windowWidth="22360" windowHeight="13710" activeTab="1" xr2:uid="{04F796B3-9D76-4BC0-BCDC-4708D1ACB929}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,13 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={87B9C53B-7C12-4514-9D95-493861D69A0F}</author>
+    <author>tc={CE3BDADF-052A-4063-8391-B0830DD4EE97}</author>
+    <author>tc={1803110A-58D4-4832-B99A-8C6E6C0601B6}</author>
+    <author>tc={243DFFE1-D1A3-4050-B2D9-E25F40D3AB59}</author>
+    <author>tc={CCBDB0C0-0734-4B0F-8DC7-399D5D9B5901}</author>
+    <author>tc={4A956656-68D2-46BC-BD2B-C17E5175B1B7}</author>
+    <author>tc={69B108FD-0772-4FB4-8B61-7028684C3F30}</author>
+    <author>tc={E7223F31-499E-44A2-A55B-DCF996EB3E78}</author>
   </authors>
   <commentList>
     <comment ref="L11" authorId="0" shapeId="0" xr:uid="{87B9C53B-7C12-4514-9D95-493861D69A0F}">
@@ -49,12 +56,68 @@
     Q122 guidance: 1670-1675</t>
       </text>
     </comment>
+    <comment ref="W11" authorId="1" shapeId="0" xr:uid="{CE3BDADF-052A-4063-8391-B0830DD4EE97}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q4 guidance: 2995-3000</t>
+      </text>
+    </comment>
+    <comment ref="X11" authorId="2" shapeId="0" xr:uid="{1803110A-58D4-4832-B99A-8C6E6C0601B6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q1 guidance: 3030-3035</t>
+      </text>
+    </comment>
+    <comment ref="Y11" authorId="3" shapeId="0" xr:uid="{243DFFE1-D1A3-4050-B2D9-E25F40D3AB59}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q2 guidance: 3260-3265</t>
+      </text>
+    </comment>
+    <comment ref="Z11" authorId="4" shapeId="0" xr:uid="{CCBDB0C0-0734-4B0F-8DC7-399D5D9B5901}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q3 guidance: 3420-3430</t>
+      </text>
+    </comment>
+    <comment ref="AA11" authorId="5" shapeId="0" xr:uid="{4A956656-68D2-46BC-BD2B-C17E5175B1B7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q4 guidance: 3650-3655</t>
+      </text>
+    </comment>
+    <comment ref="AB11" authorId="6" shapeId="0" xr:uid="{69B108FD-0772-4FB4-8B61-7028684C3F30}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q1 guidance: 3815-3820</t>
+      </text>
+    </comment>
+    <comment ref="AK11" authorId="7" shapeId="0" xr:uid="{E7223F31-499E-44A2-A55B-DCF996EB3E78}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q1 guidance: 15.735-15.775B</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="111">
   <si>
     <t>Price</t>
   </si>
@@ -360,13 +423,40 @@
   </si>
   <si>
     <t>Acquisitions</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>RPO y/y</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -393,6 +483,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -464,23 +560,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>46265</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>53731</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>46265</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>55790</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>156308</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Connector 2">
+        <xdr:cNvPr id="4" name="Straight Connector 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1AA7940-E596-AAAB-B1AC-1E5874FAAF5A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B29D088-2B97-6591-3259-67B078252762}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -488,8 +584,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12477751" y="104775"/>
-          <a:ext cx="0" cy="12360729"/>
+          <a:off x="17174308" y="53731"/>
+          <a:ext cx="0" cy="10423769"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -821,15 +917,36 @@
   <threadedComment ref="L11" dT="2022-07-26T03:20:09.97" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{87B9C53B-7C12-4514-9D95-493861D69A0F}">
     <text>Q122 guidance: 1670-1675</text>
   </threadedComment>
+  <threadedComment ref="W11" dT="2026-07-22T18:38:49.36" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{CE3BDADF-052A-4063-8391-B0830DD4EE97}">
+    <text>Q4 guidance: 2995-3000</text>
+  </threadedComment>
+  <threadedComment ref="X11" dT="2026-07-22T18:37:48.65" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{1803110A-58D4-4832-B99A-8C6E6C0601B6}">
+    <text>Q1 guidance: 3030-3035</text>
+  </threadedComment>
+  <threadedComment ref="Y11" dT="2026-07-22T18:36:37.43" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{243DFFE1-D1A3-4050-B2D9-E25F40D3AB59}">
+    <text>Q2 guidance: 3260-3265</text>
+  </threadedComment>
+  <threadedComment ref="Z11" dT="2026-07-22T18:35:42.42" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{CCBDB0C0-0734-4B0F-8DC7-399D5D9B5901}">
+    <text>Q3 guidance: 3420-3430</text>
+  </threadedComment>
+  <threadedComment ref="AA11" dT="2026-07-22T18:33:22.87" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{4A956656-68D2-46BC-BD2B-C17E5175B1B7}">
+    <text>Q4 guidance: 3650-3655</text>
+  </threadedComment>
+  <threadedComment ref="AB11" dT="2026-07-22T18:33:05.74" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{69B108FD-0772-4FB4-8B61-7028684C3F30}">
+    <text>Q1 guidance: 3815-3820</text>
+  </threadedComment>
+  <threadedComment ref="AK11" dT="2026-07-22T18:30:44.09" personId="{6895C20F-8AD2-445D-89EB-074DE7D08C7E}" id="{E7223F31-499E-44A2-A55B-DCF996EB3E78}">
+    <text>Q1 guidance: 15.735-15.775B</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C29079-183A-4E00-8AC0-8BABADD9CBE7}">
   <dimension ref="B2:M24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>64</v>
       </c>
@@ -837,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>65</v>
       </c>
@@ -848,13 +965,13 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>208</v>
+        <v>1031</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>66</v>
       </c>
@@ -863,10 +980,10 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>191152</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+        <v>97945</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>67</v>
       </c>
@@ -874,44 +991,45 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>8885</v>
+        <f>2702+2480+2724+1743</f>
+        <v>9649</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K6" t="s">
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>183755</v>
+        <v>89787</v>
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" ht="13" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>75</v>
       </c>
@@ -919,72 +1037,72 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>89</v>
       </c>
@@ -996,20 +1114,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{143D2949-B187-4CCE-8902-FF8193720176}">
-  <dimension ref="A1:V71"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AK73"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="3"/>
+    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1070,8 +1188,35 @@
       <c r="V2" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AK2">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>68</v>
       </c>
@@ -1092,7 +1237,7 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>69</v>
       </c>
@@ -1113,7 +1258,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>70</v>
       </c>
@@ -1134,7 +1279,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -1148,7 +1293,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>92</v>
       </c>
@@ -1167,7 +1312,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>90</v>
       </c>
@@ -1185,8 +1330,30 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
-    </row>
-    <row r="9" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V8" s="2">
+        <v>22300</v>
+      </c>
+      <c r="W8" s="2">
+        <v>22100</v>
+      </c>
+      <c r="X8" s="2">
+        <v>23900</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>24300</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>28200</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>27700</v>
+      </c>
+      <c r="AB8" s="2">
+        <f>+AA8+2000</f>
+        <v>29700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>71</v>
       </c>
@@ -1207,7 +1374,7 @@
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>72</v>
       </c>
@@ -1218,7 +1385,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1243,11 +1410,56 @@
       <c r="P11" s="2">
         <v>2075</v>
       </c>
+      <c r="Q11" s="2">
+        <v>2216</v>
+      </c>
+      <c r="R11" s="2">
+        <v>2365</v>
+      </c>
+      <c r="S11" s="2">
+        <v>2523</v>
+      </c>
       <c r="T11" s="2">
         <v>2542</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U11" s="2">
+        <v>2715</v>
+      </c>
+      <c r="V11" s="2">
+        <v>2866</v>
+      </c>
+      <c r="W11" s="2">
+        <v>3005</v>
+      </c>
+      <c r="X11" s="2">
+        <v>3113</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>3299</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>3466</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>3671</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>3877</v>
+      </c>
+      <c r="AC11" s="2">
+        <f>4120-AC12</f>
+        <v>4012</v>
+      </c>
+      <c r="AD11" s="2">
+        <f>4370-AD12</f>
+        <v>4268</v>
+      </c>
+      <c r="AK11" s="2">
+        <f>SUM(AA11:AD11)</f>
+        <v>15828</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1270,11 +1482,57 @@
       <c r="P12" s="2">
         <v>75</v>
       </c>
+      <c r="Q12" s="2">
+        <v>72</v>
+      </c>
+      <c r="R12" s="2">
+        <v>72</v>
+      </c>
+      <c r="S12" s="2">
+        <v>80</v>
+      </c>
       <c r="T12" s="2">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U12" s="2">
+        <v>82</v>
+      </c>
+      <c r="V12" s="2">
+        <v>91</v>
+      </c>
+      <c r="W12" s="2">
+        <v>83</v>
+      </c>
+      <c r="X12" s="2">
+        <v>102</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>108</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>102</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB12" s="2">
+        <f>+X12</f>
+        <v>102</v>
+      </c>
+      <c r="AC12" s="2">
+        <f>+Y12</f>
+        <v>108</v>
+      </c>
+      <c r="AD12" s="2">
+        <f>+Z12</f>
+        <v>102</v>
+      </c>
+      <c r="AK12" s="2">
+        <f>SUM(AA12:AD12)</f>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
@@ -1315,22 +1573,65 @@
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2288</v>
       </c>
       <c r="R13" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2437</v>
       </c>
       <c r="S13" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2603</v>
       </c>
       <c r="T13" s="7">
         <f>+T11+T12</f>
         <v>2627</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U13" s="7">
+        <f t="shared" ref="U13:AD13" si="1">+U11+U12</f>
+        <v>2797</v>
+      </c>
+      <c r="V13" s="7">
+        <f t="shared" si="1"/>
+        <v>2957</v>
+      </c>
+      <c r="W13" s="7">
+        <f t="shared" si="1"/>
+        <v>3088</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="1"/>
+        <v>3215</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="1"/>
+        <v>3407</v>
+      </c>
+      <c r="Z13" s="7">
+        <f t="shared" si="1"/>
+        <v>3568</v>
+      </c>
+      <c r="AA13" s="7">
+        <f t="shared" si="1"/>
+        <v>3770</v>
+      </c>
+      <c r="AB13" s="7">
+        <v>3987</v>
+      </c>
+      <c r="AC13" s="7">
+        <f t="shared" si="1"/>
+        <v>4120</v>
+      </c>
+      <c r="AD13" s="7">
+        <f t="shared" si="1"/>
+        <v>4370</v>
+      </c>
+      <c r="AK13" s="7">
+        <f t="shared" ref="AK13" si="2">+AK11+AK12</f>
+        <v>16239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1354,11 +1655,53 @@
       <c r="P14" s="2">
         <v>471</v>
       </c>
+      <c r="Q14" s="2">
+        <v>496</v>
+      </c>
+      <c r="R14" s="2">
+        <v>516</v>
+      </c>
+      <c r="S14" s="2">
+        <v>520</v>
+      </c>
       <c r="T14" s="2">
         <v>552</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U14" s="2">
+        <v>584</v>
+      </c>
+      <c r="V14" s="2">
+        <v>631</v>
+      </c>
+      <c r="W14" s="2">
+        <v>651</v>
+      </c>
+      <c r="X14" s="2">
+        <v>724</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>774</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>834</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>940</v>
+      </c>
+      <c r="AB14" s="2">
+        <f>+AB13-AB15</f>
+        <v>996.75</v>
+      </c>
+      <c r="AC14" s="2">
+        <f>+AC13-AC15</f>
+        <v>1030</v>
+      </c>
+      <c r="AD14" s="2">
+        <f>+AD13-AD15</f>
+        <v>1092.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
@@ -1381,15 +1724,67 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="P15" s="2">
-        <f>+P13-P14</f>
+        <f t="shared" ref="P15:U15" si="3">+P13-P14</f>
         <v>1679</v>
       </c>
+      <c r="Q15" s="2">
+        <f t="shared" si="3"/>
+        <v>1792</v>
+      </c>
+      <c r="R15" s="2">
+        <f t="shared" si="3"/>
+        <v>1921</v>
+      </c>
+      <c r="S15" s="2">
+        <f t="shared" si="3"/>
+        <v>2083</v>
+      </c>
       <c r="T15" s="2">
-        <f>+T13-T14</f>
+        <f t="shared" si="3"/>
         <v>2075</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U15" s="2">
+        <f t="shared" si="3"/>
+        <v>2213</v>
+      </c>
+      <c r="V15" s="2">
+        <f t="shared" ref="V15:Z15" si="4">+V13-V14</f>
+        <v>2326</v>
+      </c>
+      <c r="W15" s="2">
+        <f t="shared" si="4"/>
+        <v>2437</v>
+      </c>
+      <c r="X15" s="2">
+        <f t="shared" si="4"/>
+        <v>2491</v>
+      </c>
+      <c r="Y15" s="2">
+        <f t="shared" si="4"/>
+        <v>2633</v>
+      </c>
+      <c r="Z15" s="2">
+        <f t="shared" si="4"/>
+        <v>2734</v>
+      </c>
+      <c r="AA15" s="2">
+        <f>+AA13-AA14</f>
+        <v>2830</v>
+      </c>
+      <c r="AB15" s="2">
+        <f>+AB13*0.75</f>
+        <v>2990.25</v>
+      </c>
+      <c r="AC15" s="2">
+        <f>+AC13*0.75</f>
+        <v>3090</v>
+      </c>
+      <c r="AD15" s="2">
+        <f>+AD13*0.75</f>
+        <v>3277.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1412,11 +1807,53 @@
       <c r="P16" s="2">
         <v>832</v>
       </c>
+      <c r="Q16" s="2">
+        <v>799</v>
+      </c>
+      <c r="R16" s="2">
+        <v>847</v>
+      </c>
+      <c r="S16" s="2">
+        <v>923</v>
+      </c>
       <c r="T16" s="2">
         <v>960</v>
       </c>
-    </row>
-    <row r="17" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U16" s="2">
+        <v>944</v>
+      </c>
+      <c r="V16" s="2">
+        <v>1027</v>
+      </c>
+      <c r="W16" s="2">
+        <v>1054</v>
+      </c>
+      <c r="X16" s="2">
+        <v>1128</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>1056</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>1150</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>1216</v>
+      </c>
+      <c r="AB16" s="2">
+        <f t="shared" ref="AB16:AB18" si="5">+X16</f>
+        <v>1128</v>
+      </c>
+      <c r="AC16" s="2">
+        <f t="shared" ref="AC16:AC18" si="6">+Y16</f>
+        <v>1056</v>
+      </c>
+      <c r="AD16" s="2">
+        <f t="shared" ref="AD16:AD18" si="7">+Z16</f>
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1439,11 +1876,53 @@
       <c r="P17" s="2">
         <v>521</v>
       </c>
+      <c r="Q17" s="2">
+        <v>549</v>
+      </c>
+      <c r="R17" s="2">
+        <v>562</v>
+      </c>
+      <c r="S17" s="2">
+        <v>606</v>
+      </c>
       <c r="T17" s="2">
         <v>643</v>
       </c>
-    </row>
-    <row r="18" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U17" s="2">
+        <v>626</v>
+      </c>
+      <c r="V17" s="2">
+        <v>668</v>
+      </c>
+      <c r="W17" s="2">
+        <v>703</v>
+      </c>
+      <c r="X17" s="2">
+        <v>734</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>750</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>773</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>823</v>
+      </c>
+      <c r="AB17" s="2">
+        <f t="shared" si="5"/>
+        <v>734</v>
+      </c>
+      <c r="AC17" s="2">
+        <f t="shared" si="6"/>
+        <v>750</v>
+      </c>
+      <c r="AD17" s="2">
+        <f t="shared" si="7"/>
+        <v>773</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -1466,11 +1945,53 @@
       <c r="P18" s="2">
         <v>209</v>
       </c>
+      <c r="Q18" s="2">
+        <v>213</v>
+      </c>
+      <c r="R18" s="2">
+        <v>242</v>
+      </c>
+      <c r="S18" s="2">
+        <v>222</v>
+      </c>
       <c r="T18" s="2">
         <v>232</v>
       </c>
-    </row>
-    <row r="19" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U18" s="2">
+        <v>225</v>
+      </c>
+      <c r="V18" s="2">
+        <v>257</v>
+      </c>
+      <c r="W18" s="2">
+        <v>229</v>
+      </c>
+      <c r="X18" s="2">
+        <v>271</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>288</v>
+      </c>
+      <c r="AB18" s="2">
+        <f>+X18</f>
+        <v>271</v>
+      </c>
+      <c r="AC18" s="2">
+        <f>+Y18</f>
+        <v>255</v>
+      </c>
+      <c r="AD18" s="2">
+        <f>+Z18</f>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="19" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1496,12 +2017,64 @@
         <f>SUM(P16:P18)</f>
         <v>1562</v>
       </c>
+      <c r="Q19" s="2">
+        <f>SUM(Q16:Q18)</f>
+        <v>1561</v>
+      </c>
+      <c r="R19" s="2">
+        <f>SUM(R16:R18)</f>
+        <v>1651</v>
+      </c>
+      <c r="S19" s="2">
+        <f>SUM(S16:S18)</f>
+        <v>1751</v>
+      </c>
       <c r="T19" s="2">
         <f>SUM(T16:T18)</f>
         <v>1835</v>
       </c>
-    </row>
-    <row r="20" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U19" s="2">
+        <f t="shared" ref="U19:AD19" si="8">SUM(U16:U18)</f>
+        <v>1795</v>
+      </c>
+      <c r="V19" s="2">
+        <f t="shared" si="8"/>
+        <v>1952</v>
+      </c>
+      <c r="W19" s="2">
+        <f t="shared" si="8"/>
+        <v>1986</v>
+      </c>
+      <c r="X19" s="2">
+        <f t="shared" si="8"/>
+        <v>2133</v>
+      </c>
+      <c r="Y19" s="2">
+        <f t="shared" si="8"/>
+        <v>2061</v>
+      </c>
+      <c r="Z19" s="2">
+        <f t="shared" si="8"/>
+        <v>2291</v>
+      </c>
+      <c r="AA19" s="2">
+        <f t="shared" si="8"/>
+        <v>2327</v>
+      </c>
+      <c r="AB19" s="2">
+        <f t="shared" si="8"/>
+        <v>2133</v>
+      </c>
+      <c r="AC19" s="2">
+        <f t="shared" si="8"/>
+        <v>2061</v>
+      </c>
+      <c r="AD19" s="2">
+        <f t="shared" si="8"/>
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="20" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
@@ -1527,12 +2100,64 @@
         <f>P15-P19</f>
         <v>117</v>
       </c>
+      <c r="Q20" s="2">
+        <f>Q15-Q19</f>
+        <v>231</v>
+      </c>
+      <c r="R20" s="2">
+        <f>R15-R19</f>
+        <v>270</v>
+      </c>
+      <c r="S20" s="2">
+        <f>S15-S19</f>
+        <v>332</v>
+      </c>
       <c r="T20" s="2">
         <f>T15-T19</f>
         <v>240</v>
       </c>
-    </row>
-    <row r="21" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U20" s="2">
+        <f t="shared" ref="U20:AD20" si="9">U15-U19</f>
+        <v>418</v>
+      </c>
+      <c r="V20" s="2">
+        <f t="shared" si="9"/>
+        <v>374</v>
+      </c>
+      <c r="W20" s="2">
+        <f t="shared" si="9"/>
+        <v>451</v>
+      </c>
+      <c r="X20" s="2">
+        <f t="shared" si="9"/>
+        <v>358</v>
+      </c>
+      <c r="Y20" s="2">
+        <f t="shared" si="9"/>
+        <v>572</v>
+      </c>
+      <c r="Z20" s="2">
+        <f t="shared" si="9"/>
+        <v>443</v>
+      </c>
+      <c r="AA20" s="2">
+        <f t="shared" si="9"/>
+        <v>503</v>
+      </c>
+      <c r="AB20" s="2">
+        <f t="shared" si="9"/>
+        <v>857.25</v>
+      </c>
+      <c r="AC20" s="2">
+        <f t="shared" si="9"/>
+        <v>1029</v>
+      </c>
+      <c r="AD20" s="2">
+        <f t="shared" si="9"/>
+        <v>986.5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
@@ -1558,12 +2183,54 @@
         <f>74-17</f>
         <v>57</v>
       </c>
+      <c r="Q21" s="2">
+        <v>82</v>
+      </c>
+      <c r="R21" s="2">
+        <v>86</v>
+      </c>
+      <c r="S21" s="2">
+        <v>101</v>
+      </c>
       <c r="T21" s="2">
         <f>104-10</f>
         <v>94</v>
       </c>
-    </row>
-    <row r="22" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U21" s="2">
+        <v>108</v>
+      </c>
+      <c r="V21" s="2">
+        <v>106</v>
+      </c>
+      <c r="W21" s="2">
+        <v>115</v>
+      </c>
+      <c r="X21" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>115</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>105</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>88</v>
+      </c>
+      <c r="AB21" s="2">
+        <f>+AA21</f>
+        <v>88</v>
+      </c>
+      <c r="AC21" s="2">
+        <f>+AB21</f>
+        <v>88</v>
+      </c>
+      <c r="AD21" s="2">
+        <f>+AC21</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>32</v>
       </c>
@@ -1589,12 +2256,64 @@
         <f>+P20+P21</f>
         <v>174</v>
       </c>
+      <c r="Q22" s="2">
+        <f>+Q20+Q21</f>
+        <v>313</v>
+      </c>
+      <c r="R22" s="2">
+        <f>+R20+R21</f>
+        <v>356</v>
+      </c>
+      <c r="S22" s="2">
+        <f>+S20+S21</f>
+        <v>433</v>
+      </c>
       <c r="T22" s="2">
         <f>+T20+T21</f>
         <v>334</v>
       </c>
-    </row>
-    <row r="23" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U22" s="2">
+        <f t="shared" ref="U22:AD22" si="10">+U20+U21</f>
+        <v>526</v>
+      </c>
+      <c r="V22" s="2">
+        <f t="shared" si="10"/>
+        <v>480</v>
+      </c>
+      <c r="W22" s="2">
+        <f t="shared" si="10"/>
+        <v>566</v>
+      </c>
+      <c r="X22" s="2">
+        <f t="shared" si="10"/>
+        <v>474</v>
+      </c>
+      <c r="Y22" s="2">
+        <f t="shared" si="10"/>
+        <v>687</v>
+      </c>
+      <c r="Z22" s="2">
+        <f t="shared" si="10"/>
+        <v>548</v>
+      </c>
+      <c r="AA22" s="2">
+        <f t="shared" si="10"/>
+        <v>591</v>
+      </c>
+      <c r="AB22" s="2">
+        <f t="shared" si="10"/>
+        <v>945.25</v>
+      </c>
+      <c r="AC22" s="2">
+        <f t="shared" si="10"/>
+        <v>1117</v>
+      </c>
+      <c r="AD22" s="2">
+        <f t="shared" si="10"/>
+        <v>1074.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>31</v>
       </c>
@@ -1617,11 +2336,53 @@
       <c r="P23" s="2">
         <v>0</v>
       </c>
+      <c r="Q23" s="2">
+        <v>57</v>
+      </c>
+      <c r="R23" s="2">
+        <v>52</v>
+      </c>
+      <c r="S23" s="2">
+        <v>78</v>
+      </c>
       <c r="T23" s="2">
         <v>72</v>
       </c>
-    </row>
-    <row r="24" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U23" s="2">
+        <v>84</v>
+      </c>
+      <c r="V23" s="2">
+        <v>79</v>
+      </c>
+      <c r="W23" s="2">
+        <v>95</v>
+      </c>
+      <c r="X23" s="2">
+        <v>86</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>192</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>140</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>204</v>
+      </c>
+      <c r="AB23" s="2">
+        <f>+AB22*0.15</f>
+        <v>141.78749999999999</v>
+      </c>
+      <c r="AC23" s="2">
+        <f>+AC22*0.15</f>
+        <v>167.54999999999998</v>
+      </c>
+      <c r="AD23" s="2">
+        <f>+AD22*0.15</f>
+        <v>161.17499999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>30</v>
       </c>
@@ -1647,12 +2408,64 @@
         <f>+P22-P23</f>
         <v>174</v>
       </c>
+      <c r="Q24" s="2">
+        <f>+Q22-Q23</f>
+        <v>256</v>
+      </c>
+      <c r="R24" s="2">
+        <f>+R22-R23</f>
+        <v>304</v>
+      </c>
+      <c r="S24" s="2">
+        <f>+S22-S23</f>
+        <v>355</v>
+      </c>
       <c r="T24" s="2">
         <f>+T22-T23</f>
         <v>262</v>
       </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="2">
+        <f t="shared" ref="U24:AD24" si="11">+U22-U23</f>
+        <v>442</v>
+      </c>
+      <c r="V24" s="2">
+        <f t="shared" si="11"/>
+        <v>401</v>
+      </c>
+      <c r="W24" s="2">
+        <f t="shared" si="11"/>
+        <v>471</v>
+      </c>
+      <c r="X24" s="2">
+        <f t="shared" si="11"/>
+        <v>388</v>
+      </c>
+      <c r="Y24" s="2">
+        <f t="shared" si="11"/>
+        <v>495</v>
+      </c>
+      <c r="Z24" s="2">
+        <f t="shared" si="11"/>
+        <v>408</v>
+      </c>
+      <c r="AA24" s="2">
+        <f t="shared" si="11"/>
+        <v>387</v>
+      </c>
+      <c r="AB24" s="2">
+        <f t="shared" si="11"/>
+        <v>803.46249999999998</v>
+      </c>
+      <c r="AC24" s="2">
+        <f t="shared" si="11"/>
+        <v>949.45</v>
+      </c>
+      <c r="AD24" s="2">
+        <f t="shared" si="11"/>
+        <v>913.32500000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>29</v>
       </c>
@@ -1665,15 +2478,67 @@
         <v>0.36982248520710059</v>
       </c>
       <c r="P25" s="1">
-        <f>+P24/P26</f>
-        <v>0.84878048780487803</v>
+        <f t="shared" ref="P25:U25" si="12">+P24/P26</f>
+        <v>0.16975609756097562</v>
+      </c>
+      <c r="Q25" s="1">
+        <f t="shared" si="12"/>
+        <v>0.24820993130596236</v>
+      </c>
+      <c r="R25" s="1">
+        <f t="shared" si="12"/>
+        <v>0.29090909090909089</v>
+      </c>
+      <c r="S25" s="1">
+        <f t="shared" si="12"/>
+        <v>0.34186552647291074</v>
       </c>
       <c r="T25" s="1">
-        <f>+T24/T26</f>
-        <v>1.2596153846153846</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="12"/>
+        <v>0.25192307692307692</v>
+      </c>
+      <c r="U25" s="1">
+        <f t="shared" si="12"/>
+        <v>0.42387510069431128</v>
+      </c>
+      <c r="V25" s="1">
+        <f t="shared" ref="V25:Z25" si="13">+V24/V26</f>
+        <v>0.38299904489016234</v>
+      </c>
+      <c r="W25" s="1">
+        <f t="shared" si="13"/>
+        <v>0.44992033257805303</v>
+      </c>
+      <c r="X25" s="1">
+        <f t="shared" si="13"/>
+        <v>0.37072070780902144</v>
+      </c>
+      <c r="Y25" s="1">
+        <f t="shared" si="13"/>
+        <v>0.47254242142192304</v>
+      </c>
+      <c r="Z25" s="1">
+        <f t="shared" si="13"/>
+        <v>0.38968481375358166</v>
+      </c>
+      <c r="AA25" s="1">
+        <f>+AA24/AA26</f>
+        <v>0.37215689442283945</v>
+      </c>
+      <c r="AB25" s="1">
+        <f t="shared" ref="AB25:AD25" si="14">+AB24/AB26</f>
+        <v>0.77264627593077684</v>
+      </c>
+      <c r="AC25" s="1">
+        <f t="shared" si="14"/>
+        <v>0.91303453077458641</v>
+      </c>
+      <c r="AD25" s="1">
+        <f t="shared" si="14"/>
+        <v>0.87829507906651128</v>
+      </c>
+    </row>
+    <row r="26" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>1</v>
       </c>
@@ -1693,14 +2558,68 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
+      <c r="O26" s="2">
+        <f>207*5</f>
+        <v>1035</v>
+      </c>
       <c r="P26" s="2">
-        <v>205</v>
+        <f>205*5</f>
+        <v>1025</v>
+      </c>
+      <c r="Q26" s="2">
+        <f>206.277*5</f>
+        <v>1031.385</v>
+      </c>
+      <c r="R26" s="2">
+        <f>209*5</f>
+        <v>1045</v>
+      </c>
+      <c r="S26" s="2">
+        <f>207.684*5</f>
+        <v>1038.42</v>
       </c>
       <c r="T26" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.2">
+        <f>208*5</f>
+        <v>1040</v>
+      </c>
+      <c r="U26" s="2">
+        <f>208.552*5</f>
+        <v>1042.76</v>
+      </c>
+      <c r="V26" s="2">
+        <v>1047</v>
+      </c>
+      <c r="W26" s="2">
+        <v>1046.8520000000001</v>
+      </c>
+      <c r="X26" s="2">
+        <f>209.322*5</f>
+        <v>1046.6100000000001</v>
+      </c>
+      <c r="Y26" s="2">
+        <f>209.505*5</f>
+        <v>1047.5250000000001</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>1047</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>1039.884</v>
+      </c>
+      <c r="AB26" s="2">
+        <f>+AA26</f>
+        <v>1039.884</v>
+      </c>
+      <c r="AC26" s="2">
+        <f>+AB26</f>
+        <v>1039.884</v>
+      </c>
+      <c r="AD26" s="2">
+        <f>+AC26</f>
+        <v>1039.884</v>
+      </c>
+    </row>
+    <row r="28" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>48</v>
       </c>
@@ -1709,441 +2628,592 @@
         <v>0.26617647058823524</v>
       </c>
       <c r="T28" s="11">
-        <f>+T13/P13-1</f>
+        <f t="shared" ref="T28:AD28" si="15">+T13/P13-1</f>
         <v>0.22186046511627899</v>
       </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+      <c r="U28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.222465034965035</v>
+      </c>
+      <c r="V28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.21337710299548629</v>
+      </c>
+      <c r="W28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.18632347291586626</v>
+      </c>
+      <c r="X28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.22382946326608288</v>
+      </c>
+      <c r="Y28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.21809081158383981</v>
+      </c>
+      <c r="Z28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.20662833953331083</v>
+      </c>
+      <c r="AA28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.22085492227979264</v>
+      </c>
+      <c r="AB28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.2401244167962675</v>
+      </c>
+      <c r="AC28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.20927502201350157</v>
+      </c>
+      <c r="AD28" s="11">
+        <f t="shared" si="15"/>
+        <v>0.22477578475336313</v>
+      </c>
+    </row>
+    <row r="29" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z29" s="11">
+        <f>+Z8/V8-1</f>
+        <v>0.26457399103139023</v>
+      </c>
+      <c r="AA29" s="11">
+        <f>+AA8/W8-1</f>
+        <v>0.25339366515837103</v>
+      </c>
+      <c r="AB29" s="11">
+        <f>+AB8/X8-1</f>
+        <v>0.2426778242677825</v>
+      </c>
+    </row>
+    <row r="30" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U30" s="11">
+        <f t="shared" ref="U30:AA30" si="16">+U15/U13</f>
+        <v>0.79120486235252052</v>
+      </c>
+      <c r="V30" s="11">
+        <f t="shared" si="16"/>
+        <v>0.78660804869800471</v>
+      </c>
+      <c r="W30" s="11">
+        <f t="shared" si="16"/>
+        <v>0.78918393782383423</v>
+      </c>
+      <c r="X30" s="11">
+        <f t="shared" si="16"/>
+        <v>0.77480559875583199</v>
+      </c>
+      <c r="Y30" s="11">
+        <f t="shared" si="16"/>
+        <v>0.77282066334018196</v>
+      </c>
+      <c r="Z30" s="11">
+        <f t="shared" si="16"/>
+        <v>0.76625560538116588</v>
+      </c>
+      <c r="AA30" s="11">
+        <f>+AA15/AA13</f>
+        <v>0.75066312997347484</v>
+      </c>
+      <c r="AB30" s="11">
+        <f t="shared" ref="AB30:AD30" si="17">+AB15/AB13</f>
+        <v>0.75</v>
+      </c>
+      <c r="AC30" s="11">
+        <f t="shared" si="17"/>
+        <v>0.75</v>
+      </c>
+      <c r="AD30" s="11">
+        <f t="shared" si="17"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="31" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="11"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
         <v>3</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K32" s="5">
         <f>2252+1762+1484</f>
         <v>5498</v>
       </c>
-      <c r="T30" s="2">
+      <c r="T32" s="2">
         <f>2159+3254+3472</f>
         <v>8885</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>34</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K33" s="5">
         <v>824</v>
       </c>
-      <c r="T31" s="2">
+      <c r="T33" s="2">
         <v>1518</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K34" s="5">
         <f>322+655</f>
         <v>977</v>
       </c>
-      <c r="T32" s="2">
+      <c r="T34" s="2">
         <f>482+928</f>
         <v>1410</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>37</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K35" s="5">
         <v>282</v>
       </c>
-      <c r="T33" s="2">
+      <c r="T35" s="2">
         <v>608</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>38</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K36" s="5">
         <v>798</v>
       </c>
-      <c r="T34" s="2">
+      <c r="T36" s="2">
         <v>1606</v>
       </c>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>39</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K37" s="5">
         <v>583</v>
       </c>
-      <c r="T35" s="2">
+      <c r="T37" s="2">
         <v>675</v>
       </c>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>40</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K38" s="5">
         <f>266+774</f>
         <v>1040</v>
       </c>
-      <c r="T36" s="2">
+      <c r="T38" s="2">
         <f>220+1239</f>
         <v>1459</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>31</v>
       </c>
-      <c r="K37" s="5">
+      <c r="K39" s="5">
         <v>686</v>
       </c>
-      <c r="T37" s="2">
+      <c r="T39" s="2">
         <v>1447</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K40" s="5">
         <v>305</v>
       </c>
-      <c r="T38" s="2">
+      <c r="T40" s="2">
         <v>599</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>36</v>
       </c>
-      <c r="K39" s="5">
-        <f>SUM(K30:K38)</f>
+      <c r="K41" s="5">
+        <f>SUM(K32:K40)</f>
         <v>10993</v>
       </c>
-      <c r="T39" s="2">
-        <f>SUM(T30:T38)</f>
+      <c r="T41" s="2">
+        <f>SUM(T32:T40)</f>
         <v>18207</v>
       </c>
     </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>44</v>
       </c>
-      <c r="K41" s="5">
+      <c r="K43" s="5">
         <v>166</v>
       </c>
-      <c r="T41" s="2">
+      <c r="T43" s="2">
         <v>296</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
         <v>45</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K44" s="5">
         <v>661</v>
       </c>
-      <c r="T42" s="2">
+      <c r="T44" s="2">
         <v>1163</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
         <v>46</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K45" s="5">
         <f>3850+57</f>
         <v>3907</v>
       </c>
-      <c r="T43" s="2">
+      <c r="T45" s="2">
         <f>5615+85</f>
         <v>5700</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
         <v>39</v>
       </c>
-      <c r="K44" s="5">
+      <c r="K46" s="5">
         <f>87+548</f>
         <v>635</v>
       </c>
-      <c r="T44" s="2">
+      <c r="T46" s="2">
         <f>98+669</f>
         <v>767</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="5">
+      <c r="K47" s="5">
         <f>88+1484</f>
         <v>1572</v>
       </c>
-      <c r="T45" s="2">
+      <c r="T47" s="2">
         <v>1488</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
         <v>47</v>
       </c>
-      <c r="K46" s="5">
+      <c r="K48" s="5">
         <v>55</v>
       </c>
-      <c r="T46" s="2">
+      <c r="T48" s="2">
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>43</v>
       </c>
-      <c r="K47" s="5">
+      <c r="K49" s="5">
         <v>3997</v>
       </c>
-      <c r="T47" s="2">
+      <c r="T49" s="2">
         <v>8666</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
         <v>42</v>
       </c>
-      <c r="K48" s="5">
-        <f>SUM(K41:K47)</f>
+      <c r="K50" s="5">
+        <f>SUM(K43:K49)</f>
         <v>10993</v>
       </c>
-      <c r="T48" s="2">
-        <f>SUM(T41:T47)</f>
+      <c r="T50" s="2">
+        <f>SUM(T43:T49)</f>
         <v>18207</v>
       </c>
     </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>49</v>
       </c>
-      <c r="K51" s="5">
+      <c r="K53" s="5">
         <f>+Model!K24</f>
         <v>75</v>
       </c>
-      <c r="T51" s="2">
+      <c r="T53" s="2">
         <f>+T24</f>
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>50</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K54" s="3">
         <v>75</v>
       </c>
-      <c r="T52">
+      <c r="T54">
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
+    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>51</v>
       </c>
-      <c r="K53" s="3">
+      <c r="K55" s="3">
         <v>101</v>
       </c>
-      <c r="T53">
+      <c r="T55">
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
         <v>52</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K56" s="3">
         <v>83</v>
       </c>
-      <c r="T54">
+      <c r="T56">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
         <v>53</v>
       </c>
-      <c r="K55" s="3">
+      <c r="K57" s="3">
         <v>325</v>
       </c>
-      <c r="T55">
+      <c r="T57">
         <v>444</v>
       </c>
     </row>
-    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
+    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
         <v>31</v>
       </c>
-      <c r="K56" s="3">
+      <c r="K58" s="3">
         <v>-2</v>
       </c>
-      <c r="T56">
+      <c r="T58">
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
         <v>41</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K59" s="3">
         <v>15</v>
       </c>
-      <c r="T57">
+      <c r="T59">
         <v>-7</v>
       </c>
     </row>
-    <row r="58" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
+    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
         <v>54</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K60" s="3">
         <f>562-137-46+69+21-203</f>
         <v>266</v>
       </c>
-      <c r="T58">
+      <c r="T60">
         <f>-216-141-146+65-82+149</f>
         <v>-371</v>
       </c>
     </row>
-    <row r="59" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
+    <row r="61" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K59" s="5">
-        <f>SUM(K52:K58)</f>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5">
+        <f>SUM(K54:K60)</f>
         <v>863</v>
       </c>
-      <c r="T59">
-        <f>SUM(T52:T58)</f>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="R61" s="2">
+        <f>3398-Q61-P61-O61</f>
+        <v>3398</v>
+      </c>
+      <c r="S61" s="2">
+        <v>1341</v>
+      </c>
+      <c r="T61" s="2">
+        <f>SUM(T54:T60)</f>
         <v>620</v>
       </c>
-    </row>
-    <row r="61" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
+      <c r="U61" s="2">
+        <f>2632-T61-S61</f>
+        <v>671</v>
+      </c>
+      <c r="V61" s="2">
+        <f>4267-U61-T61-S61</f>
+        <v>1635</v>
+      </c>
+      <c r="W61" s="2">
+        <v>1677</v>
+      </c>
+      <c r="X61" s="2">
+        <f>2393-W61</f>
+        <v>716</v>
+      </c>
+      <c r="Y61" s="2">
+        <f>3206-X61-W61</f>
+        <v>813</v>
+      </c>
+      <c r="Z61" s="2">
+        <f>5444-Y61-X61-W61</f>
+        <v>2238</v>
+      </c>
+      <c r="AA61" s="2">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
         <v>56</v>
       </c>
-      <c r="K61" s="3">
+      <c r="K63" s="3">
         <v>-93</v>
       </c>
-      <c r="T61">
+      <c r="T63">
         <v>-262</v>
       </c>
     </row>
-    <row r="62" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
+    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
         <v>101</v>
       </c>
-      <c r="T62">
+      <c r="T64">
         <f>-31-9</f>
         <v>-40</v>
       </c>
     </row>
-    <row r="63" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B63" t="s">
+    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
         <v>57</v>
       </c>
-      <c r="K63" s="3">
+      <c r="K65" s="3">
         <f>-662-101+577-1</f>
         <v>-187</v>
       </c>
-      <c r="T63">
+      <c r="T65">
         <f>-1055-46+1040-8</f>
         <v>-69</v>
       </c>
     </row>
-    <row r="64" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B64" t="s">
+    <row r="66" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
         <v>58</v>
       </c>
-      <c r="K64" s="3">
-        <f>SUM(K61:K63)</f>
+      <c r="K66" s="3">
+        <f>SUM(K63:K65)</f>
         <v>-280</v>
       </c>
-      <c r="T64">
-        <f>SUM(T61:T63)</f>
+      <c r="T66">
+        <f>SUM(T63:T65)</f>
         <v>-371</v>
       </c>
     </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
+    <row r="68" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>59</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K68" s="3">
         <v>-6</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>60</v>
-      </c>
-      <c r="K67" s="3">
-        <v>105</v>
-      </c>
-      <c r="T67">
-        <v>-137</v>
-      </c>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B68" t="s">
-        <v>31</v>
-      </c>
-      <c r="K68" s="3">
-        <v>-150</v>
       </c>
       <c r="T68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
+        <v>60</v>
+      </c>
+      <c r="K69" s="3">
+        <v>105</v>
+      </c>
+      <c r="T69">
+        <v>-137</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70" s="3">
+        <v>-150</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
         <v>61</v>
       </c>
-      <c r="K69" s="3">
-        <f>SUM(K66:K68)</f>
+      <c r="K71" s="3">
+        <f>SUM(K68:K70)</f>
         <v>-51</v>
       </c>
-      <c r="T69">
-        <f>SUM(T66:T68)</f>
+      <c r="T71">
+        <f>SUM(T68:T70)</f>
         <v>-137</v>
       </c>
     </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B70" t="s">
+    <row r="72" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
         <v>62</v>
       </c>
-      <c r="K70" s="3">
+      <c r="K72" s="3">
         <v>-5</v>
       </c>
-      <c r="T70">
+      <c r="T72">
         <v>-9</v>
       </c>
     </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
         <v>63</v>
       </c>
-      <c r="K71" s="5">
-        <f>+K69+K70+K64+K59</f>
+      <c r="K73" s="5">
+        <f>+K71+K72+K66+K61</f>
         <v>527</v>
       </c>
-      <c r="T71">
-        <f>+T69+T64+T59+T70</f>
+      <c r="T73">
+        <f>+T71+T66+T61+T72</f>
         <v>103</v>
       </c>
     </row>
